--- a/results/LCA/lci_comparison_ab/lithium_LCIA-results.xlsx
+++ b/results/LCA/lci_comparison_ab/lithium_LCIA-results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="51">
   <si>
     <t>index</t>
   </si>
@@ -43,124 +43,130 @@
     <t>IMPACT World+ Damage 2.1 for ecoinvent v3.10 | Human health | Total human health</t>
   </si>
   <si>
-    <t>li commodities | lithium (Li) global market | GLO | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>lithium carbonate, battery grade | market for lithium carbonate, battery grade | World | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>li brine | [M+C] Lithium (Li) brine concentration (Salar de Olaroz) | AR | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>li brine | [M+C] Lithium (Li) brine concentration (Salar de Cauchari) | AR | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>battery-grade Li2CO3 | spodumene ore mining in Australia/Greenbushes and Li2CO3 production in China/Shehong | CN | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>spodumene | market for spodumene | World | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>li brine | [M+C] Lithium (Li) brine concentration (Salar del Hombre Muerto) | AR | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>lithium carbonate | lithium carbonate production, from concentrated brine | GLO | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>li content | lithium (Li) global market (Li content) | GLO | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>lithium carbonate | lithium carbonate production, from spodumene | CA | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>battery-grade LiOH.H2O | spodumene ore mining in Australia/Greenbushes and LiOH.H2O production in China/Shehong | CN | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>lithium hydroxide, battery grade | market for lithium hydroxide, battery grade | World | kilogram | premise_generated_db_2025_L</t>
+    <t>spodumene concentrate | [M+C] Spodumene ore mining and concentration | AU | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>li brine | [M+C] Lithium (Li) brine concentration (Salar de Atacama) | CL | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>lithium carbonate | lithium carbonate production, from spodumene | CA | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>li commodities | lithium (Li) global market | GLO | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>li brine | [M+C] Lithium (Li) brine concentration (Salar de Cauchari) | AR | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>lithium hydroxide, battery grade | lithium hydroxide production, battery grade | CA | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>spodumene | spodumene production | CA | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>li brine | [M+C] Lithium (Li) brine purification and concentration (Chaerhan) | CN | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>lithium carbonate, battery grade | market for lithium carbonate, battery grade | World | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>li brine | [M+C] Lithium (Li) brine concentration (Salar del Hombre Muerto) | AR | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>li brine | [M+C] Lithium (Li) brine concentration (Salar de Olaroz) | AR | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>lithium hydroxide, battery grade | market for lithium hydroxide, battery grade | World | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>spodumene | market for spodumene | World | kilogram | premise_db_2025_L</t>
   </si>
   <si>
     <t>kilogram</t>
   </si>
   <si>
+    <t>spodumene concentrate</t>
+  </si>
+  <si>
+    <t>li brine</t>
+  </si>
+  <si>
+    <t>lithium carbonate</t>
+  </si>
+  <si>
     <t>li commodities</t>
   </si>
   <si>
+    <t>lithium hydroxide, battery grade</t>
+  </si>
+  <si>
+    <t>spodumene</t>
+  </si>
+  <si>
     <t>lithium carbonate, battery grade</t>
   </si>
   <si>
-    <t>li brine</t>
-  </si>
-  <si>
-    <t>battery-grade Li2CO3</t>
-  </si>
-  <si>
-    <t>spodumene</t>
-  </si>
-  <si>
-    <t>lithium carbonate</t>
-  </si>
-  <si>
-    <t>li content</t>
-  </si>
-  <si>
-    <t>battery-grade LiOH.H2O</t>
-  </si>
-  <si>
-    <t>lithium hydroxide, battery grade</t>
+    <t>[M+C] Spodumene ore mining and concentration</t>
+  </si>
+  <si>
+    <t>[M+C] Lithium (Li) brine concentration (Salar de Atacama)</t>
+  </si>
+  <si>
+    <t>lithium carbonate production, from spodumene</t>
   </si>
   <si>
     <t>lithium (Li) global market</t>
   </si>
   <si>
+    <t>[M+C] Lithium (Li) brine concentration (Salar de Cauchari)</t>
+  </si>
+  <si>
+    <t>lithium hydroxide production, battery grade</t>
+  </si>
+  <si>
+    <t>spodumene production</t>
+  </si>
+  <si>
+    <t>[M+C] Lithium (Li) brine purification and concentration (Chaerhan)</t>
+  </si>
+  <si>
     <t>market for lithium carbonate, battery grade</t>
   </si>
   <si>
+    <t>[M+C] Lithium (Li) brine concentration (Salar del Hombre Muerto)</t>
+  </si>
+  <si>
     <t>[M+C] Lithium (Li) brine concentration (Salar de Olaroz)</t>
   </si>
   <si>
-    <t>[M+C] Lithium (Li) brine concentration (Salar de Cauchari)</t>
-  </si>
-  <si>
-    <t>spodumene ore mining in Australia/Greenbushes and Li2CO3 production in China/Shehong</t>
+    <t>market for lithium hydroxide, battery grade</t>
   </si>
   <si>
     <t>market for spodumene</t>
   </si>
   <si>
-    <t>[M+C] Lithium (Li) brine concentration (Salar del Hombre Muerto)</t>
-  </si>
-  <si>
-    <t>lithium carbonate production, from concentrated brine</t>
-  </si>
-  <si>
-    <t>lithium (Li) global market (Li content)</t>
-  </si>
-  <si>
-    <t>lithium carbonate production, from spodumene</t>
-  </si>
-  <si>
-    <t>spodumene ore mining in Australia/Greenbushes and LiOH.H2O production in China/Shehong</t>
-  </si>
-  <si>
-    <t>market for lithium hydroxide, battery grade</t>
+    <t>AU</t>
+  </si>
+  <si>
+    <t>CL</t>
+  </si>
+  <si>
+    <t>CA</t>
   </si>
   <si>
     <t>GLO</t>
   </si>
   <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
     <t>World</t>
   </si>
   <si>
-    <t>AR</t>
-  </si>
-  <si>
-    <t>CN</t>
-  </si>
-  <si>
-    <t>CA</t>
-  </si>
-  <si>
-    <t>premise_generated_db_2025_L</t>
+    <t>premise_db_2025_L</t>
   </si>
 </sst>
 </file>
@@ -518,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -561,25 +567,25 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s">
         <v>43</v>
       </c>
       <c r="H2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I2">
-        <v>13.66566229458781</v>
+        <v>0.9914835888911927</v>
       </c>
       <c r="J2">
-        <v>0.0001296763066759286</v>
+        <v>8.162177339995662E-06</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -593,25 +599,25 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G3" t="s">
         <v>44</v>
       </c>
       <c r="H3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I3">
-        <v>8.939095437277849</v>
+        <v>0.3066308150511873</v>
       </c>
       <c r="J3">
-        <v>8.473673333784041E-05</v>
+        <v>4.829183926150911E-06</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -625,25 +631,25 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G4" t="s">
         <v>45</v>
       </c>
       <c r="H4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I4">
-        <v>0.2317210034938103</v>
+        <v>7.090268626259636</v>
       </c>
       <c r="J4">
-        <v>2.189348317115496E-06</v>
+        <v>5.903799154524237E-05</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -657,25 +663,25 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I5">
-        <v>0.8768299104751968</v>
+        <v>14.1601784965387</v>
       </c>
       <c r="J5">
-        <v>6.373487409337066E-06</v>
+        <v>0.0001305008494137098</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -689,25 +695,25 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I6">
-        <v>24.39667054456872</v>
+        <v>0.8516419704823239</v>
       </c>
       <c r="J6">
-        <v>0.0002161988979840976</v>
+        <v>6.121685950171104E-06</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -721,25 +727,25 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I7">
-        <v>0.07607776439709753</v>
+        <v>7.594287703751797</v>
       </c>
       <c r="J7">
-        <v>2.581674607833338E-07</v>
+        <v>7.381187382684841E-05</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -753,25 +759,25 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G8" t="s">
         <v>45</v>
       </c>
       <c r="H8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I8">
-        <v>0.1347450156415807</v>
+        <v>0.07612845384172837</v>
       </c>
       <c r="J8">
-        <v>1.276437057846646E-06</v>
+        <v>2.440750156762307E-07</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -785,25 +791,25 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G9" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="H9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I9">
-        <v>1.593153892485504</v>
+        <v>1.729516558248106</v>
       </c>
       <c r="J9">
-        <v>1.394051605187381E-05</v>
+        <v>1.750310883126852E-05</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -817,25 +823,25 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G10" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="H10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I10">
-        <v>73.59538245584449</v>
+        <v>9.3169831956063</v>
       </c>
       <c r="J10">
-        <v>0.0006984873643253667</v>
+        <v>8.444491994507379E-05</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -849,25 +855,25 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G11" t="s">
         <v>47</v>
       </c>
       <c r="H11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I11">
-        <v>5.529884156268936</v>
+        <v>0.1350014485355611</v>
       </c>
       <c r="J11">
-        <v>5.308578505971897E-05</v>
+        <v>1.271591037985587E-06</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -881,25 +887,25 @@
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I12">
-        <v>15.88278325044887</v>
+        <v>0.2318163469632679</v>
       </c>
       <c r="J12">
-        <v>0.0001415785630734736</v>
+        <v>2.181034782636706E-06</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -913,25 +919,57 @@
         <v>1</v>
       </c>
       <c r="D13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" t="s">
+        <v>50</v>
+      </c>
+      <c r="I13">
+        <v>7.694027628265104</v>
+      </c>
+      <c r="J13">
+        <v>7.484996020569412E-05</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
         <v>21</v>
       </c>
-      <c r="E13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" t="s">
         <v>42</v>
       </c>
-      <c r="G13" t="s">
-        <v>44</v>
-      </c>
-      <c r="H13" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13">
-        <v>7.671542553718634</v>
-      </c>
-      <c r="J13">
-        <v>7.661314319501373E-05</v>
+      <c r="G14" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14" t="s">
+        <v>50</v>
+      </c>
+      <c r="I14">
+        <v>0.07900827895838708</v>
+      </c>
+      <c r="J14">
+        <v>2.664769119285453E-07</v>
       </c>
     </row>
   </sheetData>

--- a/results/LCA/lci_comparison_ab/lithium_LCIA-results.xlsx
+++ b/results/LCA/lci_comparison_ab/lithium_LCIA-results.xlsx
@@ -1,15 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/fasc_metal_sustainability/results/LCA/lci_comparison_ab/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_161140F9F613C8264F2C4C5A45CAC6AE52387E24" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74B95D29-5B80-41DA-975F-9052D3C34075}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$1</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -172,8 +194,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -190,12 +212,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -225,24 +259,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -280,7 +330,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -314,6 +364,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -348,9 +399,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -523,11 +575,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="108.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="60.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -556,44 +620,44 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2">
+        <v>0.85164197048232393</v>
+      </c>
+      <c r="J2">
+        <v>6.1216859501711043E-6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>9</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I2">
-        <v>0.9914835888911927</v>
-      </c>
-      <c r="J2">
-        <v>8.162177339995662E-06</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -605,118 +669,118 @@
         <v>24</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H3" t="s">
         <v>50</v>
       </c>
       <c r="I3">
-        <v>0.3066308150511873</v>
+        <v>0.13500144853556109</v>
       </c>
       <c r="J3">
-        <v>4.829183926150911E-06</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1">
+        <v>1.271591037985587E-6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0.23181634696326789</v>
+      </c>
+      <c r="J4" s="3">
+        <v>2.1810347826367059E-6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>0</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0.9914835888911927</v>
+      </c>
+      <c r="J5" s="3">
+        <v>8.1621773399956623E-6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="C6" s="3">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I4">
-        <v>7.090268626259636</v>
-      </c>
-      <c r="J4">
-        <v>5.903799154524237E-05</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" t="s">
-        <v>50</v>
-      </c>
-      <c r="I5">
-        <v>14.1601784965387</v>
-      </c>
-      <c r="J5">
-        <v>0.0001305008494137098</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" t="s">
-        <v>47</v>
-      </c>
-      <c r="H6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6">
-        <v>0.8516419704823239</v>
-      </c>
-      <c r="J6">
-        <v>6.121685950171104E-06</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="H6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" s="3">
+        <v>7.0902686262596362</v>
+      </c>
+      <c r="J6" s="3">
+        <v>5.9037991545242367E-5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -742,13 +806,13 @@
         <v>50</v>
       </c>
       <c r="I7">
-        <v>7.594287703751797</v>
+        <v>7.5942877037517968</v>
       </c>
       <c r="J7">
-        <v>7.381187382684841E-05</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>7.3811873826848406E-5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -774,18 +838,18 @@
         <v>50</v>
       </c>
       <c r="I8">
-        <v>0.07612845384172837</v>
+        <v>7.6128453841728366E-2</v>
       </c>
       <c r="J8">
-        <v>2.440750156762307E-07</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>2.4407501567623068E-7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -797,150 +861,150 @@
         <v>24</v>
       </c>
       <c r="F9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9">
+        <v>0.30663081505118728</v>
+      </c>
+      <c r="J9">
+        <v>4.8291839261509114E-6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" t="s">
         <v>37</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G10" t="s">
         <v>48</v>
       </c>
-      <c r="H9" t="s">
-        <v>50</v>
-      </c>
-      <c r="I9">
+      <c r="H10" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10">
         <v>1.729516558248106</v>
       </c>
-      <c r="J9">
-        <v>1.750310883126852E-05</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="1">
+      <c r="J10">
+        <v>1.7503108831268519E-5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>3</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I11" s="3">
+        <v>14.1601784965387</v>
+      </c>
+      <c r="J11" s="3">
+        <v>1.3050084941370981E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
         <v>8</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="C12" s="5">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G12" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="H10" t="s">
-        <v>50</v>
-      </c>
-      <c r="I10">
-        <v>9.3169831956063</v>
-      </c>
-      <c r="J10">
-        <v>8.444491994507379E-05</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H11" t="s">
-        <v>50</v>
-      </c>
-      <c r="I11">
-        <v>0.1350014485355611</v>
-      </c>
-      <c r="J11">
-        <v>1.271591037985587E-06</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G12" t="s">
-        <v>47</v>
-      </c>
-      <c r="H12" t="s">
-        <v>50</v>
-      </c>
-      <c r="I12">
-        <v>0.2318163469632679</v>
-      </c>
-      <c r="J12">
-        <v>2.181034782636706E-06</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="1">
+      <c r="H12" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I12" s="5">
+        <v>9.3169831956062996</v>
+      </c>
+      <c r="J12" s="5">
+        <v>8.4444919945073793E-5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
         <v>11</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="C13" s="5">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="H13" t="s">
-        <v>50</v>
-      </c>
-      <c r="I13">
-        <v>7.694027628265104</v>
-      </c>
-      <c r="J13">
-        <v>7.484996020569412E-05</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="H13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I13" s="5">
+        <v>7.6940276282651041</v>
+      </c>
+      <c r="J13" s="5">
+        <v>7.4849960205694118E-5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -966,13 +1030,18 @@
         <v>50</v>
       </c>
       <c r="I14">
-        <v>0.07900827895838708</v>
+        <v>7.9008278958387079E-2</v>
       </c>
       <c r="J14">
-        <v>2.664769119285453E-07</v>
+        <v>2.6647691192854532E-7</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J14">
+      <sortCondition ref="G1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>